--- a/data/derived_data/4_Diversities/ps_16S_rare_expe_D1_mtd_table.xlsx
+++ b/data/derived_data/4_Diversities/ps_16S_rare_expe_D1_mtd_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -185,12 +185,24 @@
     <t xml:space="preserve">MS_025</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_027</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_028</t>
   </si>
   <si>
     <t xml:space="preserve">MS_030</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_035</t>
   </si>
   <si>
@@ -206,6 +218,9 @@
     <t xml:space="preserve">MS_038</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_039</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_040</t>
   </si>
   <si>
@@ -233,6 +248,12 @@
     <t xml:space="preserve">MS_060</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_064</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_065</t>
   </si>
   <si>
@@ -254,21 +275,48 @@
     <t xml:space="preserve">MS_072</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larvae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DaughterLarva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_090</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_091</t>
   </si>
   <si>
-    <t xml:space="preserve">Larvae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DaughterLarva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Larva</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_092</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_100</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_101</t>
   </si>
   <si>
@@ -299,9 +347,6 @@
     <t xml:space="preserve">MS_122</t>
   </si>
   <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
     <t xml:space="preserve">MS_123</t>
   </si>
   <si>
@@ -332,6 +377,9 @@
     <t xml:space="preserve">MS_137</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_138</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_141</t>
   </si>
   <si>
@@ -356,6 +404,9 @@
     <t xml:space="preserve">MS_146</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_153</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_155</t>
   </si>
   <si>
@@ -386,6 +437,9 @@
     <t xml:space="preserve">MS_166</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_168</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_169</t>
   </si>
   <si>
@@ -398,6 +452,9 @@
     <t xml:space="preserve">MS_173</t>
   </si>
   <si>
+    <t xml:space="preserve">MS_265</t>
+  </si>
+  <si>
     <t xml:space="preserve">MS_266</t>
   </si>
   <si>
@@ -405,6 +462,9 @@
   </si>
   <si>
     <t xml:space="preserve">MS_268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS_269</t>
   </si>
   <si>
     <t xml:space="preserve">MS_271</t>
@@ -1249,10 +1309,10 @@
         <v>29</v>
       </c>
       <c r="L9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N9" t="s">
         <v>26</v>
@@ -1278,7 +1338,7 @@
         <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
@@ -1302,16 +1362,16 @@
         <v>27</v>
       </c>
       <c r="J10" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K10" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L10" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N10" t="s">
         <v>26</v>
@@ -1337,7 +1397,7 @@
         <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
@@ -1346,7 +1406,7 @@
         <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
         <v>49</v>
@@ -1355,7 +1415,7 @@
         <v>50</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I11" t="s">
         <v>27</v>
@@ -1393,7 +1453,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
@@ -1405,7 +1465,7 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
         <v>49</v>
@@ -1414,22 +1474,22 @@
         <v>50</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I12" t="s">
         <v>27</v>
       </c>
       <c r="J12" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K12" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L12" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M12" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N12" t="s">
         <v>26</v>
@@ -1447,15 +1507,15 @@
         <v>49</v>
       </c>
       <c r="S12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
         <v>21</v>
@@ -1464,7 +1524,7 @@
         <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s">
         <v>49</v>
@@ -1473,7 +1533,7 @@
         <v>50</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I13" t="s">
         <v>27</v>
@@ -1482,13 +1542,13 @@
         <v>37</v>
       </c>
       <c r="K13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M13" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="N13" t="s">
         <v>26</v>
@@ -1506,7 +1566,7 @@
         <v>49</v>
       </c>
       <c r="S13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -1514,7 +1574,7 @@
         <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
         <v>21</v>
@@ -1523,7 +1583,7 @@
         <v>48</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
         <v>49</v>
@@ -1532,22 +1592,22 @@
         <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I14" t="s">
         <v>27</v>
       </c>
       <c r="J14" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K14" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L14" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="M14" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N14" t="s">
         <v>26</v>
@@ -1570,7 +1630,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
@@ -1582,7 +1642,7 @@
         <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F15" t="s">
         <v>49</v>
@@ -1591,22 +1651,22 @@
         <v>50</v>
       </c>
       <c r="H15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I15" t="s">
         <v>27</v>
       </c>
       <c r="J15" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K15" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="L15" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="M15" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="N15" t="s">
         <v>26</v>
@@ -1624,12 +1684,12 @@
         <v>49</v>
       </c>
       <c r="S15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
@@ -1638,34 +1698,34 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I16" t="s">
         <v>27</v>
       </c>
       <c r="J16" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K16" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L16" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N16" t="s">
         <v>26</v>
@@ -1677,18 +1737,18 @@
         <v>32</v>
       </c>
       <c r="Q16" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="R16" t="s">
+        <v>49</v>
+      </c>
+      <c r="S16" t="s">
         <v>66</v>
-      </c>
-      <c r="S16" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
@@ -1697,57 +1757,57 @@
         <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" t="s">
+        <v>38</v>
+      </c>
+      <c r="L17" t="s">
+        <v>39</v>
+      </c>
+      <c r="M17" t="s">
+        <v>40</v>
+      </c>
+      <c r="N17" t="s">
+        <v>26</v>
+      </c>
+      <c r="O17" t="s">
+        <v>26</v>
+      </c>
+      <c r="P17" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>49</v>
+      </c>
+      <c r="R17" t="s">
+        <v>49</v>
+      </c>
+      <c r="S17" t="s">
         <v>67</v>
-      </c>
-      <c r="G17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" t="s">
-        <v>51</v>
-      </c>
-      <c r="I17" t="s">
-        <v>27</v>
-      </c>
-      <c r="J17" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" t="s">
-        <v>29</v>
-      </c>
-      <c r="L17" t="s">
-        <v>34</v>
-      </c>
-      <c r="M17" t="s">
-        <v>35</v>
-      </c>
-      <c r="N17" t="s">
-        <v>26</v>
-      </c>
-      <c r="O17" t="s">
-        <v>26</v>
-      </c>
-      <c r="P17" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>26</v>
-      </c>
-      <c r="R17" t="s">
-        <v>66</v>
-      </c>
-      <c r="S17" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
@@ -1756,34 +1816,34 @@
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E18" t="s">
         <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="G18" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H18" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I18" t="s">
         <v>27</v>
       </c>
       <c r="J18" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K18" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L18" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M18" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="N18" t="s">
         <v>26</v>
@@ -1795,18 +1855,18 @@
         <v>32</v>
       </c>
       <c r="Q18" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="R18" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="S18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
@@ -1815,34 +1875,34 @@
         <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
         <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H19" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I19" t="s">
         <v>27</v>
       </c>
       <c r="J19" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K19" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L19" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M19" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="N19" t="s">
         <v>26</v>
@@ -1854,33 +1914,33 @@
         <v>32</v>
       </c>
       <c r="Q19" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="R19" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="S19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
         <v>71</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" t="s">
-        <v>66</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G20" t="s">
         <v>25</v>
@@ -1892,16 +1952,16 @@
         <v>27</v>
       </c>
       <c r="J20" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K20" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L20" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M20" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N20" t="s">
         <v>26</v>
@@ -1916,15 +1976,15 @@
         <v>26</v>
       </c>
       <c r="R20" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="S20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
@@ -1933,13 +1993,13 @@
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
         <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G21" t="s">
         <v>25</v>
@@ -1951,16 +2011,16 @@
         <v>27</v>
       </c>
       <c r="J21" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K21" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L21" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M21" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N21" t="s">
         <v>26</v>
@@ -1975,15 +2035,15 @@
         <v>26</v>
       </c>
       <c r="R21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="S21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
@@ -1992,19 +2052,19 @@
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E22" t="s">
         <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G22" t="s">
         <v>25</v>
       </c>
       <c r="H22" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I22" t="s">
         <v>27</v>
@@ -2016,10 +2076,10 @@
         <v>29</v>
       </c>
       <c r="L22" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M22" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N22" t="s">
         <v>26</v>
@@ -2034,15 +2094,15 @@
         <v>26</v>
       </c>
       <c r="R22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="S22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
         <v>20</v>
@@ -2051,19 +2111,19 @@
         <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E23" t="s">
         <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G23" t="s">
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I23" t="s">
         <v>27</v>
@@ -2075,10 +2135,10 @@
         <v>29</v>
       </c>
       <c r="L23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M23" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N23" t="s">
         <v>26</v>
@@ -2093,15 +2153,15 @@
         <v>26</v>
       </c>
       <c r="R23" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="S23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
         <v>21</v>
@@ -2110,34 +2170,34 @@
         <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E24" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G24" t="s">
         <v>25</v>
       </c>
       <c r="H24" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I24" t="s">
         <v>27</v>
       </c>
       <c r="J24" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K24" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L24" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M24" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N24" t="s">
         <v>26</v>
@@ -2152,15 +2212,15 @@
         <v>26</v>
       </c>
       <c r="R24" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="S24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
         <v>20</v>
@@ -2169,34 +2229,34 @@
         <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E25" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G25" t="s">
         <v>25</v>
       </c>
       <c r="H25" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I25" t="s">
         <v>27</v>
       </c>
       <c r="J25" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K25" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L25" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M25" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N25" t="s">
         <v>26</v>
@@ -2211,15 +2271,15 @@
         <v>26</v>
       </c>
       <c r="R25" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="S25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
         <v>21</v>
@@ -2228,34 +2288,34 @@
         <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E26" t="s">
         <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s">
         <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I26" t="s">
         <v>27</v>
       </c>
       <c r="J26" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="K26" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="L26" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M26" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N26" t="s">
         <v>26</v>
@@ -2270,15 +2330,15 @@
         <v>26</v>
       </c>
       <c r="R26" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="S26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
         <v>20</v>
@@ -2287,34 +2347,34 @@
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E27" t="s">
         <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
       </c>
       <c r="H27" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I27" t="s">
         <v>27</v>
       </c>
       <c r="J27" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="K27" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="L27" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M27" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N27" t="s">
         <v>26</v>
@@ -2329,51 +2389,51 @@
         <v>26</v>
       </c>
       <c r="R27" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="S27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
       </c>
       <c r="D28" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E28" t="s">
         <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G28" t="s">
         <v>25</v>
       </c>
       <c r="H28" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I28" t="s">
         <v>27</v>
       </c>
       <c r="J28" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K28" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="L28" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="M28" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="N28" t="s">
         <v>26</v>
@@ -2388,51 +2448,51 @@
         <v>26</v>
       </c>
       <c r="R28" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="S28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G29" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H29" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I29" t="s">
         <v>27</v>
       </c>
       <c r="J29" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K29" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L29" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M29" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N29" t="s">
         <v>26</v>
@@ -2444,113 +2504,113 @@
         <v>32</v>
       </c>
       <c r="Q29" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="R29" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="S29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
         <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E30" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30" t="s">
+        <v>31</v>
+      </c>
+      <c r="N30" t="s">
+        <v>26</v>
+      </c>
+      <c r="O30" t="s">
+        <v>26</v>
+      </c>
+      <c r="P30" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>26</v>
+      </c>
+      <c r="R30" t="s">
+        <v>71</v>
+      </c>
+      <c r="S30" t="s">
         <v>82</v>
-      </c>
-      <c r="G30" t="s">
-        <v>50</v>
-      </c>
-      <c r="H30" t="s">
-        <v>51</v>
-      </c>
-      <c r="I30" t="s">
-        <v>27</v>
-      </c>
-      <c r="J30" t="s">
-        <v>37</v>
-      </c>
-      <c r="K30" t="s">
-        <v>38</v>
-      </c>
-      <c r="L30" t="s">
-        <v>39</v>
-      </c>
-      <c r="M30" t="s">
-        <v>40</v>
-      </c>
-      <c r="N30" t="s">
-        <v>26</v>
-      </c>
-      <c r="O30" t="s">
-        <v>26</v>
-      </c>
-      <c r="P30" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>83</v>
-      </c>
-      <c r="R30" t="s">
-        <v>83</v>
-      </c>
-      <c r="S30" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
         <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E31" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F31" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G31" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H31" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I31" t="s">
         <v>27</v>
       </c>
       <c r="J31" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K31" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L31" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="M31" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N31" t="s">
         <v>26</v>
@@ -2562,39 +2622,39 @@
         <v>32</v>
       </c>
       <c r="Q31" t="s">
+        <v>26</v>
+      </c>
+      <c r="R31" t="s">
+        <v>71</v>
+      </c>
+      <c r="S31" t="s">
         <v>83</v>
-      </c>
-      <c r="R31" t="s">
-        <v>83</v>
-      </c>
-      <c r="S31" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C32" t="s">
         <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E32" t="s">
         <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G32" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H32" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I32" t="s">
         <v>27</v>
@@ -2621,142 +2681,142 @@
         <v>32</v>
       </c>
       <c r="Q32" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="R32" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="S32" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E33" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="G33" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H33" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I33" t="s">
         <v>27</v>
       </c>
       <c r="J33" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="K33" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="L33" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="M33" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="N33" t="s">
         <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="P33" t="s">
         <v>32</v>
       </c>
       <c r="Q33" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="R33" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="S33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="E34" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="G34" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="H34" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I34" t="s">
         <v>27</v>
       </c>
       <c r="J34" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="K34" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="L34" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="M34" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="N34" t="s">
         <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P34" t="s">
         <v>32</v>
       </c>
       <c r="Q34" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="R34" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="S34" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B35" t="s">
         <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D35" t="s">
         <v>88</v>
@@ -2777,22 +2837,22 @@
         <v>27</v>
       </c>
       <c r="J35" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="K35" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="L35" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="M35" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="N35" t="s">
         <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="P35" t="s">
         <v>32</v>
@@ -2801,27 +2861,27 @@
         <v>90</v>
       </c>
       <c r="R35" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S35" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B36" t="s">
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
         <v>88</v>
       </c>
       <c r="E36" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F36" t="s">
         <v>89</v>
@@ -2851,7 +2911,7 @@
         <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P36" t="s">
         <v>32</v>
@@ -2860,27 +2920,27 @@
         <v>90</v>
       </c>
       <c r="R36" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
         <v>21</v>
       </c>
       <c r="C37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
         <v>88</v>
       </c>
       <c r="E37" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="F37" t="s">
         <v>89</v>
@@ -2901,16 +2961,16 @@
         <v>29</v>
       </c>
       <c r="L37" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M37" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N37" t="s">
         <v>26</v>
       </c>
       <c r="O37" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="P37" t="s">
         <v>32</v>
@@ -2919,27 +2979,27 @@
         <v>90</v>
       </c>
       <c r="R37" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
         <v>88</v>
       </c>
       <c r="E38" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="F38" t="s">
         <v>89</v>
@@ -2969,7 +3029,7 @@
         <v>26</v>
       </c>
       <c r="O38" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="P38" t="s">
         <v>32</v>
@@ -2978,27 +3038,27 @@
         <v>90</v>
       </c>
       <c r="R38" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S38" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B39" t="s">
         <v>21</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
         <v>88</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F39" t="s">
         <v>89</v>
@@ -3028,7 +3088,7 @@
         <v>26</v>
       </c>
       <c r="O39" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="P39" t="s">
         <v>32</v>
@@ -3037,27 +3097,27 @@
         <v>90</v>
       </c>
       <c r="R39" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
         <v>88</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F40" t="s">
         <v>89</v>
@@ -3075,19 +3135,19 @@
         <v>37</v>
       </c>
       <c r="K40" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="L40" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="M40" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="N40" t="s">
         <v>26</v>
       </c>
       <c r="O40" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="P40" t="s">
         <v>32</v>
@@ -3096,27 +3156,27 @@
         <v>90</v>
       </c>
       <c r="R40" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S40" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
         <v>21</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
         <v>88</v>
       </c>
       <c r="E41" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="F41" t="s">
         <v>89</v>
@@ -3146,7 +3206,7 @@
         <v>26</v>
       </c>
       <c r="O41" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P41" t="s">
         <v>32</v>
@@ -3155,27 +3215,27 @@
         <v>90</v>
       </c>
       <c r="R41" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
         <v>21</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
         <v>88</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="F42" t="s">
         <v>89</v>
@@ -3184,28 +3244,28 @@
         <v>50</v>
       </c>
       <c r="H42" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I42" t="s">
         <v>27</v>
       </c>
       <c r="J42" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="K42" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="L42" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="M42" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="N42" t="s">
         <v>26</v>
       </c>
       <c r="O42" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="P42" t="s">
         <v>32</v>
@@ -3214,21 +3274,21 @@
         <v>90</v>
       </c>
       <c r="R42" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S42" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B43" t="s">
         <v>21</v>
       </c>
       <c r="C43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
         <v>88</v>
@@ -3243,28 +3303,28 @@
         <v>50</v>
       </c>
       <c r="H43" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I43" t="s">
         <v>27</v>
       </c>
       <c r="J43" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="K43" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="L43" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="M43" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="N43" t="s">
         <v>26</v>
       </c>
       <c r="O43" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="P43" t="s">
         <v>32</v>
@@ -3273,27 +3333,27 @@
         <v>90</v>
       </c>
       <c r="R43" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S43" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
         <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
         <v>88</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
         <v>89</v>
@@ -3302,28 +3362,28 @@
         <v>50</v>
       </c>
       <c r="H44" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I44" t="s">
         <v>27</v>
       </c>
       <c r="J44" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="K44" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="L44" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="M44" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="N44" t="s">
         <v>26</v>
       </c>
       <c r="O44" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="P44" t="s">
         <v>32</v>
@@ -3332,27 +3392,27 @@
         <v>90</v>
       </c>
       <c r="R44" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D45" t="s">
         <v>88</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F45" t="s">
         <v>89</v>
@@ -3361,7 +3421,7 @@
         <v>50</v>
       </c>
       <c r="H45" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I45" t="s">
         <v>27</v>
@@ -3373,16 +3433,16 @@
         <v>29</v>
       </c>
       <c r="L45" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M45" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N45" t="s">
         <v>26</v>
       </c>
       <c r="O45" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="P45" t="s">
         <v>32</v>
@@ -3391,27 +3451,27 @@
         <v>90</v>
       </c>
       <c r="R45" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S45" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B46" t="s">
         <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D46" t="s">
         <v>88</v>
       </c>
       <c r="E46" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F46" t="s">
         <v>89</v>
@@ -3420,28 +3480,28 @@
         <v>50</v>
       </c>
       <c r="H46" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I46" t="s">
         <v>27</v>
       </c>
       <c r="J46" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K46" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L46" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M46" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N46" t="s">
         <v>26</v>
       </c>
       <c r="O46" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P46" t="s">
         <v>32</v>
@@ -3450,27 +3510,27 @@
         <v>90</v>
       </c>
       <c r="R46" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S46" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D47" t="s">
         <v>88</v>
       </c>
       <c r="E47" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F47" t="s">
         <v>89</v>
@@ -3479,28 +3539,28 @@
         <v>50</v>
       </c>
       <c r="H47" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I47" t="s">
         <v>27</v>
       </c>
       <c r="J47" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K47" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L47" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M47" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N47" t="s">
         <v>26</v>
       </c>
       <c r="O47" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="P47" t="s">
         <v>32</v>
@@ -3509,15 +3569,15 @@
         <v>90</v>
       </c>
       <c r="R47" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="S47" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s">
         <v>21</v>
@@ -3526,52 +3586,52 @@
         <v>20</v>
       </c>
       <c r="D48" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E48" t="s">
         <v>43</v>
       </c>
       <c r="F48" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="G48" t="s">
         <v>50</v>
       </c>
       <c r="H48" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I48" t="s">
         <v>27</v>
       </c>
       <c r="J48" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="K48" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="L48" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M48" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N48" t="s">
         <v>26</v>
       </c>
       <c r="O48" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="P48" t="s">
         <v>32</v>
       </c>
       <c r="Q48" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="R48" t="s">
         <v>26</v>
       </c>
       <c r="S48" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49">
@@ -3585,46 +3645,46 @@
         <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E49" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="F49" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="G49" t="s">
         <v>50</v>
       </c>
       <c r="H49" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I49" t="s">
         <v>27</v>
       </c>
       <c r="J49" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="K49" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="L49" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M49" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N49" t="s">
         <v>26</v>
       </c>
       <c r="O49" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P49" t="s">
         <v>32</v>
       </c>
       <c r="Q49" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="R49" t="s">
         <v>26</v>
@@ -3644,46 +3704,46 @@
         <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E50" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F50" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="G50" t="s">
         <v>50</v>
       </c>
       <c r="H50" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I50" t="s">
         <v>27</v>
       </c>
       <c r="J50" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K50" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="L50" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="M50" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="N50" t="s">
         <v>26</v>
       </c>
       <c r="O50" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="P50" t="s">
         <v>32</v>
       </c>
       <c r="Q50" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="R50" t="s">
         <v>26</v>
@@ -3703,13 +3763,13 @@
         <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E51" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="F51" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G51" t="s">
         <v>50</v>
@@ -3721,28 +3781,28 @@
         <v>27</v>
       </c>
       <c r="J51" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="K51" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="L51" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="M51" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="N51" t="s">
         <v>26</v>
       </c>
       <c r="O51" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="P51" t="s">
         <v>32</v>
       </c>
       <c r="Q51" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R51" t="s">
         <v>26</v>
@@ -3753,7 +3813,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B52" t="s">
         <v>21</v>
@@ -3762,13 +3822,13 @@
         <v>20</v>
       </c>
       <c r="D52" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E52" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="F52" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G52" t="s">
         <v>50</v>
@@ -3780,39 +3840,39 @@
         <v>27</v>
       </c>
       <c r="J52" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="K52" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="L52" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="M52" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="N52" t="s">
         <v>26</v>
       </c>
       <c r="O52" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="P52" t="s">
         <v>32</v>
       </c>
       <c r="Q52" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R52" t="s">
         <v>26</v>
       </c>
       <c r="S52" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B53" t="s">
         <v>21</v>
@@ -3821,13 +3881,13 @@
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E53" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="F53" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G53" t="s">
         <v>50</v>
@@ -3839,39 +3899,39 @@
         <v>27</v>
       </c>
       <c r="J53" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K53" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L53" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="M53" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N53" t="s">
         <v>26</v>
       </c>
       <c r="O53" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="P53" t="s">
         <v>32</v>
       </c>
       <c r="Q53" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R53" t="s">
         <v>26</v>
       </c>
       <c r="S53" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B54" t="s">
         <v>21</v>
@@ -3880,13 +3940,13 @@
         <v>20</v>
       </c>
       <c r="D54" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E54" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F54" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G54" t="s">
         <v>50</v>
@@ -3919,18 +3979,18 @@
         <v>32</v>
       </c>
       <c r="Q54" t="s">
+        <v>106</v>
+      </c>
+      <c r="R54" t="s">
+        <v>26</v>
+      </c>
+      <c r="S54" t="s">
         <v>112</v>
-      </c>
-      <c r="R54" t="s">
-        <v>26</v>
-      </c>
-      <c r="S54" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B55" t="s">
         <v>21</v>
@@ -3939,13 +3999,13 @@
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E55" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F55" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G55" t="s">
         <v>50</v>
@@ -3978,18 +4038,18 @@
         <v>32</v>
       </c>
       <c r="Q55" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R55" t="s">
         <v>26</v>
       </c>
       <c r="S55" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B56" t="s">
         <v>21</v>
@@ -3998,13 +4058,13 @@
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E56" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F56" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G56" t="s">
         <v>50</v>
@@ -4037,18 +4097,18 @@
         <v>32</v>
       </c>
       <c r="Q56" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R56" t="s">
         <v>26</v>
       </c>
       <c r="S56" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B57" t="s">
         <v>21</v>
@@ -4057,13 +4117,13 @@
         <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E57" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F57" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G57" t="s">
         <v>50</v>
@@ -4096,18 +4156,18 @@
         <v>32</v>
       </c>
       <c r="Q57" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R57" t="s">
         <v>26</v>
       </c>
       <c r="S57" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B58" t="s">
         <v>21</v>
@@ -4116,19 +4176,19 @@
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E58" t="s">
         <v>23</v>
       </c>
       <c r="F58" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G58" t="s">
         <v>50</v>
       </c>
       <c r="H58" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I58" t="s">
         <v>27</v>
@@ -4149,24 +4209,24 @@
         <v>26</v>
       </c>
       <c r="O58" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="P58" t="s">
         <v>32</v>
       </c>
       <c r="Q58" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R58" t="s">
         <v>26</v>
       </c>
       <c r="S58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
         <v>21</v>
@@ -4175,57 +4235,57 @@
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E59" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F59" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G59" t="s">
         <v>50</v>
       </c>
       <c r="H59" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I59" t="s">
         <v>27</v>
       </c>
       <c r="J59" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="K59" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="L59" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="M59" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="N59" t="s">
         <v>26</v>
       </c>
       <c r="O59" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="P59" t="s">
         <v>32</v>
       </c>
       <c r="Q59" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R59" t="s">
         <v>26</v>
       </c>
       <c r="S59" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B60" t="s">
         <v>21</v>
@@ -4234,19 +4294,19 @@
         <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E60" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F60" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G60" t="s">
         <v>50</v>
       </c>
       <c r="H60" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I60" t="s">
         <v>27</v>
@@ -4267,24 +4327,24 @@
         <v>26</v>
       </c>
       <c r="O60" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="P60" t="s">
         <v>32</v>
       </c>
       <c r="Q60" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R60" t="s">
         <v>26</v>
       </c>
       <c r="S60" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B61" t="s">
         <v>21</v>
@@ -4293,19 +4353,19 @@
         <v>20</v>
       </c>
       <c r="D61" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E61" t="s">
         <v>43</v>
       </c>
       <c r="F61" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G61" t="s">
         <v>50</v>
       </c>
       <c r="H61" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I61" t="s">
         <v>27</v>
@@ -4326,24 +4386,24 @@
         <v>26</v>
       </c>
       <c r="O61" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P61" t="s">
         <v>32</v>
       </c>
       <c r="Q61" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R61" t="s">
         <v>26</v>
       </c>
       <c r="S61" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B62" t="s">
         <v>21</v>
@@ -4352,19 +4412,19 @@
         <v>20</v>
       </c>
       <c r="D62" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E62" t="s">
         <v>43</v>
       </c>
       <c r="F62" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G62" t="s">
         <v>50</v>
       </c>
       <c r="H62" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I62" t="s">
         <v>27</v>
@@ -4376,33 +4436,33 @@
         <v>29</v>
       </c>
       <c r="L62" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M62" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N62" t="s">
         <v>26</v>
       </c>
       <c r="O62" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="P62" t="s">
         <v>32</v>
       </c>
       <c r="Q62" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R62" t="s">
         <v>26</v>
       </c>
       <c r="S62" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
         <v>21</v>
@@ -4411,34 +4471,34 @@
         <v>20</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E63" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F63" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G63" t="s">
         <v>50</v>
       </c>
       <c r="H63" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I63" t="s">
         <v>27</v>
       </c>
       <c r="J63" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K63" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L63" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="M63" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="N63" t="s">
         <v>26</v>
@@ -4450,18 +4510,18 @@
         <v>32</v>
       </c>
       <c r="Q63" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R63" t="s">
         <v>26</v>
       </c>
       <c r="S63" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B64" t="s">
         <v>21</v>
@@ -4470,19 +4530,19 @@
         <v>20</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E64" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F64" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G64" t="s">
         <v>50</v>
       </c>
       <c r="H64" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I64" t="s">
         <v>27</v>
@@ -4509,18 +4569,18 @@
         <v>32</v>
       </c>
       <c r="Q64" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R64" t="s">
         <v>26</v>
       </c>
       <c r="S64" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B65" t="s">
         <v>21</v>
@@ -4529,19 +4589,19 @@
         <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E65" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F65" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G65" t="s">
         <v>50</v>
       </c>
       <c r="H65" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I65" t="s">
         <v>27</v>
@@ -4568,18 +4628,18 @@
         <v>32</v>
       </c>
       <c r="Q65" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R65" t="s">
         <v>26</v>
       </c>
       <c r="S65" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B66" t="s">
         <v>21</v>
@@ -4588,19 +4648,19 @@
         <v>20</v>
       </c>
       <c r="D66" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E66" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F66" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G66" t="s">
         <v>50</v>
       </c>
       <c r="H66" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I66" t="s">
         <v>27</v>
@@ -4621,39 +4681,39 @@
         <v>26</v>
       </c>
       <c r="O66" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="P66" t="s">
         <v>32</v>
       </c>
       <c r="Q66" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="R66" t="s">
         <v>26</v>
       </c>
       <c r="S66" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B67" t="s">
         <v>21</v>
       </c>
       <c r="C67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E67" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="F67" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="G67" t="s">
         <v>50</v>
@@ -4665,34 +4725,34 @@
         <v>27</v>
       </c>
       <c r="J67" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="K67" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="L67" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="M67" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="N67" t="s">
         <v>26</v>
       </c>
       <c r="O67" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="P67" t="s">
         <v>32</v>
       </c>
       <c r="Q67" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="R67" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="S67" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68">
@@ -4703,16 +4763,16 @@
         <v>21</v>
       </c>
       <c r="C68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E68" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="F68" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="G68" t="s">
         <v>50</v>
@@ -4724,31 +4784,31 @@
         <v>27</v>
       </c>
       <c r="J68" t="s">
+        <v>52</v>
+      </c>
+      <c r="K68" t="s">
+        <v>53</v>
+      </c>
+      <c r="L68" t="s">
+        <v>54</v>
+      </c>
+      <c r="M68" t="s">
+        <v>55</v>
+      </c>
+      <c r="N68" t="s">
+        <v>26</v>
+      </c>
+      <c r="O68" t="s">
         <v>28</v>
       </c>
-      <c r="K68" t="s">
-        <v>29</v>
-      </c>
-      <c r="L68" t="s">
-        <v>30</v>
-      </c>
-      <c r="M68" t="s">
-        <v>31</v>
-      </c>
-      <c r="N68" t="s">
-        <v>26</v>
-      </c>
-      <c r="O68" t="s">
-        <v>26</v>
-      </c>
       <c r="P68" t="s">
         <v>32</v>
       </c>
       <c r="Q68" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="R68" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="S68" t="s">
         <v>129</v>
@@ -4762,16 +4822,16 @@
         <v>21</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D69" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E69" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F69" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="G69" t="s">
         <v>50</v>
@@ -4783,31 +4843,31 @@
         <v>27</v>
       </c>
       <c r="J69" t="s">
+        <v>28</v>
+      </c>
+      <c r="K69" t="s">
+        <v>29</v>
+      </c>
+      <c r="L69" t="s">
+        <v>30</v>
+      </c>
+      <c r="M69" t="s">
+        <v>31</v>
+      </c>
+      <c r="N69" t="s">
+        <v>26</v>
+      </c>
+      <c r="O69" t="s">
         <v>37</v>
       </c>
-      <c r="K69" t="s">
-        <v>38</v>
-      </c>
-      <c r="L69" t="s">
-        <v>39</v>
-      </c>
-      <c r="M69" t="s">
-        <v>40</v>
-      </c>
-      <c r="N69" t="s">
-        <v>26</v>
-      </c>
-      <c r="O69" t="s">
-        <v>26</v>
-      </c>
       <c r="P69" t="s">
         <v>32</v>
       </c>
       <c r="Q69" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="R69" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="S69" t="s">
         <v>130</v>
@@ -4821,22 +4881,22 @@
         <v>21</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E70" t="s">
         <v>20</v>
       </c>
       <c r="F70" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="G70" t="s">
         <v>50</v>
       </c>
       <c r="H70" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I70" t="s">
         <v>27</v>
@@ -4857,16 +4917,16 @@
         <v>26</v>
       </c>
       <c r="O70" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P70" t="s">
         <v>32</v>
       </c>
       <c r="Q70" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="R70" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="S70" t="s">
         <v>131</v>
@@ -4880,52 +4940,52 @@
         <v>21</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E71" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="F71" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="G71" t="s">
         <v>50</v>
       </c>
       <c r="H71" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I71" t="s">
         <v>27</v>
       </c>
       <c r="J71" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="K71" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="L71" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M71" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N71" t="s">
         <v>26</v>
       </c>
       <c r="O71" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="P71" t="s">
         <v>32</v>
       </c>
       <c r="Q71" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="R71" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="S71" t="s">
         <v>132</v>
@@ -4939,22 +4999,22 @@
         <v>21</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D72" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E72" t="s">
         <v>23</v>
       </c>
       <c r="F72" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="G72" t="s">
         <v>50</v>
       </c>
       <c r="H72" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I72" t="s">
         <v>27</v>
@@ -4975,19 +5035,1199 @@
         <v>26</v>
       </c>
       <c r="O72" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="P72" t="s">
         <v>32</v>
       </c>
       <c r="Q72" t="s">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="R72" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="S72" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>134</v>
+      </c>
+      <c r="B73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C73" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" t="s">
+        <v>126</v>
+      </c>
+      <c r="E73" t="s">
+        <v>23</v>
+      </c>
+      <c r="F73" t="s">
+        <v>127</v>
+      </c>
+      <c r="G73" t="s">
+        <v>50</v>
+      </c>
+      <c r="H73" t="s">
+        <v>51</v>
+      </c>
+      <c r="I73" t="s">
+        <v>27</v>
+      </c>
+      <c r="J73" t="s">
+        <v>37</v>
+      </c>
+      <c r="K73" t="s">
+        <v>44</v>
+      </c>
+      <c r="L73" t="s">
+        <v>45</v>
+      </c>
+      <c r="M73" t="s">
+        <v>46</v>
+      </c>
+      <c r="N73" t="s">
+        <v>26</v>
+      </c>
+      <c r="O73" t="s">
+        <v>28</v>
+      </c>
+      <c r="P73" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>128</v>
+      </c>
+      <c r="R73" t="s">
+        <v>26</v>
+      </c>
+      <c r="S73" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" t="s">
+        <v>21</v>
+      </c>
+      <c r="C74" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" t="s">
+        <v>126</v>
+      </c>
+      <c r="E74" t="s">
+        <v>23</v>
+      </c>
+      <c r="F74" t="s">
+        <v>127</v>
+      </c>
+      <c r="G74" t="s">
+        <v>50</v>
+      </c>
+      <c r="H74" t="s">
+        <v>51</v>
+      </c>
+      <c r="I74" t="s">
+        <v>27</v>
+      </c>
+      <c r="J74" t="s">
+        <v>37</v>
+      </c>
+      <c r="K74" t="s">
+        <v>44</v>
+      </c>
+      <c r="L74" t="s">
+        <v>45</v>
+      </c>
+      <c r="M74" t="s">
+        <v>46</v>
+      </c>
+      <c r="N74" t="s">
+        <v>26</v>
+      </c>
+      <c r="O74" t="s">
+        <v>37</v>
+      </c>
+      <c r="P74" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>128</v>
+      </c>
+      <c r="R74" t="s">
+        <v>26</v>
+      </c>
+      <c r="S74" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>136</v>
+      </c>
+      <c r="B75" t="s">
+        <v>21</v>
+      </c>
+      <c r="C75" t="s">
+        <v>20</v>
+      </c>
+      <c r="D75" t="s">
+        <v>126</v>
+      </c>
+      <c r="E75" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75" t="s">
+        <v>127</v>
+      </c>
+      <c r="G75" t="s">
+        <v>50</v>
+      </c>
+      <c r="H75" t="s">
+        <v>64</v>
+      </c>
+      <c r="I75" t="s">
+        <v>27</v>
+      </c>
+      <c r="J75" t="s">
+        <v>52</v>
+      </c>
+      <c r="K75" t="s">
+        <v>53</v>
+      </c>
+      <c r="L75" t="s">
+        <v>54</v>
+      </c>
+      <c r="M75" t="s">
+        <v>55</v>
+      </c>
+      <c r="N75" t="s">
+        <v>26</v>
+      </c>
+      <c r="O75" t="s">
+        <v>37</v>
+      </c>
+      <c r="P75" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>128</v>
+      </c>
+      <c r="R75" t="s">
+        <v>26</v>
+      </c>
+      <c r="S75" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>137</v>
+      </c>
+      <c r="B76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" t="s">
+        <v>20</v>
+      </c>
+      <c r="D76" t="s">
+        <v>126</v>
+      </c>
+      <c r="E76" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76" t="s">
+        <v>127</v>
+      </c>
+      <c r="G76" t="s">
+        <v>50</v>
+      </c>
+      <c r="H76" t="s">
+        <v>64</v>
+      </c>
+      <c r="I76" t="s">
+        <v>27</v>
+      </c>
+      <c r="J76" t="s">
+        <v>28</v>
+      </c>
+      <c r="K76" t="s">
+        <v>29</v>
+      </c>
+      <c r="L76" t="s">
+        <v>34</v>
+      </c>
+      <c r="M76" t="s">
+        <v>35</v>
+      </c>
+      <c r="N76" t="s">
+        <v>26</v>
+      </c>
+      <c r="O76" t="s">
+        <v>52</v>
+      </c>
+      <c r="P76" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>128</v>
+      </c>
+      <c r="R76" t="s">
+        <v>26</v>
+      </c>
+      <c r="S76" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>138</v>
+      </c>
+      <c r="B77" t="s">
+        <v>21</v>
+      </c>
+      <c r="C77" t="s">
+        <v>20</v>
+      </c>
+      <c r="D77" t="s">
+        <v>126</v>
+      </c>
+      <c r="E77" t="s">
+        <v>23</v>
+      </c>
+      <c r="F77" t="s">
+        <v>127</v>
+      </c>
+      <c r="G77" t="s">
+        <v>50</v>
+      </c>
+      <c r="H77" t="s">
+        <v>64</v>
+      </c>
+      <c r="I77" t="s">
+        <v>27</v>
+      </c>
+      <c r="J77" t="s">
+        <v>28</v>
+      </c>
+      <c r="K77" t="s">
+        <v>29</v>
+      </c>
+      <c r="L77" t="s">
+        <v>34</v>
+      </c>
+      <c r="M77" t="s">
+        <v>35</v>
+      </c>
+      <c r="N77" t="s">
+        <v>26</v>
+      </c>
+      <c r="O77" t="s">
+        <v>28</v>
+      </c>
+      <c r="P77" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>128</v>
+      </c>
+      <c r="R77" t="s">
+        <v>26</v>
+      </c>
+      <c r="S77" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>139</v>
+      </c>
+      <c r="B78" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" t="s">
+        <v>126</v>
+      </c>
+      <c r="E78" t="s">
+        <v>43</v>
+      </c>
+      <c r="F78" t="s">
+        <v>127</v>
+      </c>
+      <c r="G78" t="s">
+        <v>50</v>
+      </c>
+      <c r="H78" t="s">
+        <v>64</v>
+      </c>
+      <c r="I78" t="s">
+        <v>27</v>
+      </c>
+      <c r="J78" t="s">
+        <v>28</v>
+      </c>
+      <c r="K78" t="s">
+        <v>29</v>
+      </c>
+      <c r="L78" t="s">
+        <v>34</v>
+      </c>
+      <c r="M78" t="s">
+        <v>35</v>
+      </c>
+      <c r="N78" t="s">
+        <v>26</v>
+      </c>
+      <c r="O78" t="s">
+        <v>37</v>
+      </c>
+      <c r="P78" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>128</v>
+      </c>
+      <c r="R78" t="s">
+        <v>26</v>
+      </c>
+      <c r="S78" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>140</v>
+      </c>
+      <c r="B79" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" t="s">
+        <v>126</v>
+      </c>
+      <c r="E79" t="s">
+        <v>43</v>
+      </c>
+      <c r="F79" t="s">
+        <v>127</v>
+      </c>
+      <c r="G79" t="s">
+        <v>50</v>
+      </c>
+      <c r="H79" t="s">
+        <v>64</v>
+      </c>
+      <c r="I79" t="s">
+        <v>27</v>
+      </c>
+      <c r="J79" t="s">
+        <v>28</v>
+      </c>
+      <c r="K79" t="s">
+        <v>29</v>
+      </c>
+      <c r="L79" t="s">
+        <v>30</v>
+      </c>
+      <c r="M79" t="s">
+        <v>31</v>
+      </c>
+      <c r="N79" t="s">
+        <v>26</v>
+      </c>
+      <c r="O79" t="s">
+        <v>52</v>
+      </c>
+      <c r="P79" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>128</v>
+      </c>
+      <c r="R79" t="s">
+        <v>26</v>
+      </c>
+      <c r="S79" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>141</v>
+      </c>
+      <c r="B80" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" t="s">
+        <v>20</v>
+      </c>
+      <c r="D80" t="s">
+        <v>126</v>
+      </c>
+      <c r="E80" t="s">
+        <v>43</v>
+      </c>
+      <c r="F80" t="s">
+        <v>127</v>
+      </c>
+      <c r="G80" t="s">
+        <v>50</v>
+      </c>
+      <c r="H80" t="s">
+        <v>64</v>
+      </c>
+      <c r="I80" t="s">
+        <v>27</v>
+      </c>
+      <c r="J80" t="s">
+        <v>28</v>
+      </c>
+      <c r="K80" t="s">
+        <v>29</v>
+      </c>
+      <c r="L80" t="s">
+        <v>30</v>
+      </c>
+      <c r="M80" t="s">
+        <v>31</v>
+      </c>
+      <c r="N80" t="s">
+        <v>26</v>
+      </c>
+      <c r="O80" t="s">
+        <v>37</v>
+      </c>
+      <c r="P80" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>128</v>
+      </c>
+      <c r="R80" t="s">
+        <v>26</v>
+      </c>
+      <c r="S80" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>142</v>
+      </c>
+      <c r="B81" t="s">
+        <v>21</v>
+      </c>
+      <c r="C81" t="s">
+        <v>20</v>
+      </c>
+      <c r="D81" t="s">
+        <v>126</v>
+      </c>
+      <c r="E81" t="s">
+        <v>23</v>
+      </c>
+      <c r="F81" t="s">
+        <v>127</v>
+      </c>
+      <c r="G81" t="s">
+        <v>50</v>
+      </c>
+      <c r="H81" t="s">
+        <v>64</v>
+      </c>
+      <c r="I81" t="s">
+        <v>27</v>
+      </c>
+      <c r="J81" t="s">
+        <v>37</v>
+      </c>
+      <c r="K81" t="s">
+        <v>38</v>
+      </c>
+      <c r="L81" t="s">
+        <v>39</v>
+      </c>
+      <c r="M81" t="s">
+        <v>40</v>
+      </c>
+      <c r="N81" t="s">
+        <v>26</v>
+      </c>
+      <c r="O81" t="s">
+        <v>52</v>
+      </c>
+      <c r="P81" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>128</v>
+      </c>
+      <c r="R81" t="s">
+        <v>26</v>
+      </c>
+      <c r="S81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>143</v>
+      </c>
+      <c r="B82" t="s">
+        <v>21</v>
+      </c>
+      <c r="C82" t="s">
+        <v>20</v>
+      </c>
+      <c r="D82" t="s">
+        <v>126</v>
+      </c>
+      <c r="E82" t="s">
+        <v>23</v>
+      </c>
+      <c r="F82" t="s">
+        <v>127</v>
+      </c>
+      <c r="G82" t="s">
+        <v>50</v>
+      </c>
+      <c r="H82" t="s">
+        <v>64</v>
+      </c>
+      <c r="I82" t="s">
+        <v>27</v>
+      </c>
+      <c r="J82" t="s">
+        <v>37</v>
+      </c>
+      <c r="K82" t="s">
+        <v>38</v>
+      </c>
+      <c r="L82" t="s">
+        <v>39</v>
+      </c>
+      <c r="M82" t="s">
+        <v>40</v>
+      </c>
+      <c r="N82" t="s">
+        <v>26</v>
+      </c>
+      <c r="O82" t="s">
+        <v>28</v>
+      </c>
+      <c r="P82" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>128</v>
+      </c>
+      <c r="R82" t="s">
+        <v>26</v>
+      </c>
+      <c r="S82" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>144</v>
+      </c>
+      <c r="B83" t="s">
+        <v>21</v>
+      </c>
+      <c r="C83" t="s">
+        <v>20</v>
+      </c>
+      <c r="D83" t="s">
+        <v>126</v>
+      </c>
+      <c r="E83" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83" t="s">
+        <v>127</v>
+      </c>
+      <c r="G83" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" t="s">
+        <v>64</v>
+      </c>
+      <c r="I83" t="s">
+        <v>27</v>
+      </c>
+      <c r="J83" t="s">
+        <v>37</v>
+      </c>
+      <c r="K83" t="s">
+        <v>38</v>
+      </c>
+      <c r="L83" t="s">
+        <v>39</v>
+      </c>
+      <c r="M83" t="s">
+        <v>40</v>
+      </c>
+      <c r="N83" t="s">
+        <v>26</v>
+      </c>
+      <c r="O83" t="s">
+        <v>37</v>
+      </c>
+      <c r="P83" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>128</v>
+      </c>
+      <c r="R83" t="s">
+        <v>26</v>
+      </c>
+      <c r="S83" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>145</v>
+      </c>
+      <c r="B84" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" t="s">
+        <v>20</v>
+      </c>
+      <c r="D84" t="s">
+        <v>126</v>
+      </c>
+      <c r="E84" t="s">
+        <v>23</v>
+      </c>
+      <c r="F84" t="s">
+        <v>127</v>
+      </c>
+      <c r="G84" t="s">
+        <v>50</v>
+      </c>
+      <c r="H84" t="s">
+        <v>64</v>
+      </c>
+      <c r="I84" t="s">
+        <v>27</v>
+      </c>
+      <c r="J84" t="s">
+        <v>37</v>
+      </c>
+      <c r="K84" t="s">
+        <v>44</v>
+      </c>
+      <c r="L84" t="s">
+        <v>45</v>
+      </c>
+      <c r="M84" t="s">
+        <v>46</v>
+      </c>
+      <c r="N84" t="s">
+        <v>26</v>
+      </c>
+      <c r="O84" t="s">
+        <v>28</v>
+      </c>
+      <c r="P84" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>128</v>
+      </c>
+      <c r="R84" t="s">
+        <v>26</v>
+      </c>
+      <c r="S84" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>146</v>
+      </c>
+      <c r="B85" t="s">
+        <v>21</v>
+      </c>
+      <c r="C85" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" t="s">
+        <v>48</v>
+      </c>
+      <c r="E85" t="s">
+        <v>62</v>
+      </c>
+      <c r="F85" t="s">
+        <v>49</v>
+      </c>
+      <c r="G85" t="s">
+        <v>50</v>
+      </c>
+      <c r="H85" t="s">
+        <v>51</v>
+      </c>
+      <c r="I85" t="s">
+        <v>27</v>
+      </c>
+      <c r="J85" t="s">
+        <v>52</v>
+      </c>
+      <c r="K85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L85" t="s">
+        <v>54</v>
+      </c>
+      <c r="M85" t="s">
+        <v>55</v>
+      </c>
+      <c r="N85" t="s">
+        <v>26</v>
+      </c>
+      <c r="O85" t="s">
+        <v>26</v>
+      </c>
+      <c r="P85" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>49</v>
+      </c>
+      <c r="R85" t="s">
+        <v>49</v>
+      </c>
+      <c r="S85" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>147</v>
+      </c>
+      <c r="B86" t="s">
+        <v>21</v>
+      </c>
+      <c r="C86" t="s">
+        <v>21</v>
+      </c>
+      <c r="D86" t="s">
+        <v>48</v>
+      </c>
+      <c r="E86" t="s">
+        <v>62</v>
+      </c>
+      <c r="F86" t="s">
+        <v>49</v>
+      </c>
+      <c r="G86" t="s">
+        <v>50</v>
+      </c>
+      <c r="H86" t="s">
+        <v>51</v>
+      </c>
+      <c r="I86" t="s">
+        <v>27</v>
+      </c>
+      <c r="J86" t="s">
+        <v>28</v>
+      </c>
+      <c r="K86" t="s">
+        <v>29</v>
+      </c>
+      <c r="L86" t="s">
+        <v>34</v>
+      </c>
+      <c r="M86" t="s">
+        <v>35</v>
+      </c>
+      <c r="N86" t="s">
+        <v>26</v>
+      </c>
+      <c r="O86" t="s">
+        <v>26</v>
+      </c>
+      <c r="P86" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>49</v>
+      </c>
+      <c r="R86" t="s">
+        <v>49</v>
+      </c>
+      <c r="S86" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>148</v>
+      </c>
+      <c r="B87" t="s">
+        <v>21</v>
+      </c>
+      <c r="C87" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" t="s">
+        <v>48</v>
+      </c>
+      <c r="E87" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87" t="s">
+        <v>49</v>
+      </c>
+      <c r="G87" t="s">
+        <v>50</v>
+      </c>
+      <c r="H87" t="s">
+        <v>51</v>
+      </c>
+      <c r="I87" t="s">
+        <v>27</v>
+      </c>
+      <c r="J87" t="s">
+        <v>28</v>
+      </c>
+      <c r="K87" t="s">
+        <v>29</v>
+      </c>
+      <c r="L87" t="s">
+        <v>30</v>
+      </c>
+      <c r="M87" t="s">
+        <v>31</v>
+      </c>
+      <c r="N87" t="s">
+        <v>26</v>
+      </c>
+      <c r="O87" t="s">
+        <v>26</v>
+      </c>
+      <c r="P87" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>49</v>
+      </c>
+      <c r="R87" t="s">
+        <v>49</v>
+      </c>
+      <c r="S87" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>149</v>
+      </c>
+      <c r="B88" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" t="s">
+        <v>48</v>
+      </c>
+      <c r="E88" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88" t="s">
+        <v>49</v>
+      </c>
+      <c r="G88" t="s">
+        <v>50</v>
+      </c>
+      <c r="H88" t="s">
+        <v>51</v>
+      </c>
+      <c r="I88" t="s">
+        <v>27</v>
+      </c>
+      <c r="J88" t="s">
+        <v>37</v>
+      </c>
+      <c r="K88" t="s">
+        <v>38</v>
+      </c>
+      <c r="L88" t="s">
+        <v>39</v>
+      </c>
+      <c r="M88" t="s">
+        <v>40</v>
+      </c>
+      <c r="N88" t="s">
+        <v>26</v>
+      </c>
+      <c r="O88" t="s">
+        <v>26</v>
+      </c>
+      <c r="P88" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>49</v>
+      </c>
+      <c r="R88" t="s">
+        <v>49</v>
+      </c>
+      <c r="S88" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>150</v>
+      </c>
+      <c r="B89" t="s">
+        <v>21</v>
+      </c>
+      <c r="C89" t="s">
+        <v>21</v>
+      </c>
+      <c r="D89" t="s">
+        <v>48</v>
+      </c>
+      <c r="E89" t="s">
+        <v>62</v>
+      </c>
+      <c r="F89" t="s">
+        <v>49</v>
+      </c>
+      <c r="G89" t="s">
+        <v>50</v>
+      </c>
+      <c r="H89" t="s">
+        <v>51</v>
+      </c>
+      <c r="I89" t="s">
+        <v>27</v>
+      </c>
+      <c r="J89" t="s">
+        <v>37</v>
+      </c>
+      <c r="K89" t="s">
+        <v>44</v>
+      </c>
+      <c r="L89" t="s">
+        <v>45</v>
+      </c>
+      <c r="M89" t="s">
+        <v>46</v>
+      </c>
+      <c r="N89" t="s">
+        <v>26</v>
+      </c>
+      <c r="O89" t="s">
+        <v>26</v>
+      </c>
+      <c r="P89" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>49</v>
+      </c>
+      <c r="R89" t="s">
+        <v>49</v>
+      </c>
+      <c r="S89" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>151</v>
+      </c>
+      <c r="B90" t="s">
+        <v>21</v>
+      </c>
+      <c r="C90" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" t="s">
+        <v>48</v>
+      </c>
+      <c r="E90" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90" t="s">
+        <v>49</v>
+      </c>
+      <c r="G90" t="s">
+        <v>50</v>
+      </c>
+      <c r="H90" t="s">
+        <v>64</v>
+      </c>
+      <c r="I90" t="s">
+        <v>27</v>
+      </c>
+      <c r="J90" t="s">
+        <v>37</v>
+      </c>
+      <c r="K90" t="s">
+        <v>38</v>
+      </c>
+      <c r="L90" t="s">
+        <v>39</v>
+      </c>
+      <c r="M90" t="s">
+        <v>40</v>
+      </c>
+      <c r="N90" t="s">
+        <v>26</v>
+      </c>
+      <c r="O90" t="s">
+        <v>26</v>
+      </c>
+      <c r="P90" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>49</v>
+      </c>
+      <c r="R90" t="s">
+        <v>49</v>
+      </c>
+      <c r="S90" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>152</v>
+      </c>
+      <c r="B91" t="s">
+        <v>21</v>
+      </c>
+      <c r="C91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" t="s">
+        <v>48</v>
+      </c>
+      <c r="E91" t="s">
+        <v>62</v>
+      </c>
+      <c r="F91" t="s">
+        <v>49</v>
+      </c>
+      <c r="G91" t="s">
+        <v>50</v>
+      </c>
+      <c r="H91" t="s">
+        <v>64</v>
+      </c>
+      <c r="I91" t="s">
+        <v>27</v>
+      </c>
+      <c r="J91" t="s">
+        <v>28</v>
+      </c>
+      <c r="K91" t="s">
+        <v>29</v>
+      </c>
+      <c r="L91" t="s">
+        <v>30</v>
+      </c>
+      <c r="M91" t="s">
+        <v>31</v>
+      </c>
+      <c r="N91" t="s">
+        <v>26</v>
+      </c>
+      <c r="O91" t="s">
+        <v>26</v>
+      </c>
+      <c r="P91" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>49</v>
+      </c>
+      <c r="R91" t="s">
+        <v>49</v>
+      </c>
+      <c r="S91" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>153</v>
+      </c>
+      <c r="B92" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" t="s">
+        <v>21</v>
+      </c>
+      <c r="D92" t="s">
+        <v>48</v>
+      </c>
+      <c r="E92" t="s">
+        <v>23</v>
+      </c>
+      <c r="F92" t="s">
+        <v>49</v>
+      </c>
+      <c r="G92" t="s">
+        <v>50</v>
+      </c>
+      <c r="H92" t="s">
+        <v>64</v>
+      </c>
+      <c r="I92" t="s">
+        <v>27</v>
+      </c>
+      <c r="J92" t="s">
+        <v>37</v>
+      </c>
+      <c r="K92" t="s">
+        <v>44</v>
+      </c>
+      <c r="L92" t="s">
+        <v>45</v>
+      </c>
+      <c r="M92" t="s">
+        <v>46</v>
+      </c>
+      <c r="N92" t="s">
+        <v>26</v>
+      </c>
+      <c r="O92" t="s">
+        <v>26</v>
+      </c>
+      <c r="P92" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>49</v>
+      </c>
+      <c r="R92" t="s">
+        <v>49</v>
+      </c>
+      <c r="S92" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
